--- a/tutor/家教带课记录.xlsx
+++ b/tutor/家教带课记录.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12330"/>
+    <workbookView windowWidth="28800" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="Doing" sheetId="1" r:id="rId1"/>
@@ -77,348 +77,336 @@
     <t>第10课</t>
   </si>
   <si>
+    <t xml:space="preserve">转账时间(灰色表示线上上课（课时费1小时100），绿色表示课时费已发)：
+一尔优和一对一教育当月1号和15号
+</t>
+  </si>
+  <si>
+    <t>第11课</t>
+  </si>
+  <si>
     <t>初三</t>
   </si>
   <si>
     <t>数学</t>
   </si>
   <si>
-    <t>一对一教育</t>
+    <t>新耀科技</t>
+  </si>
+  <si>
+    <t>180/1.5h</t>
+  </si>
+  <si>
+    <t>周六19：00-20：30</t>
+  </si>
+  <si>
+    <t>宁芮一</t>
+  </si>
+  <si>
+    <t>光明路北小区14-2-503</t>
+  </si>
+  <si>
+    <t>兵一</t>
+  </si>
+  <si>
+    <t>90/150</t>
+  </si>
+  <si>
+    <t>初二</t>
+  </si>
+  <si>
+    <t>豌豆文化</t>
+  </si>
+  <si>
+    <t>260/2h</t>
+  </si>
+  <si>
+    <t>周六15：30-17：30</t>
+  </si>
+  <si>
+    <t>双胞胎</t>
+  </si>
+  <si>
+    <t>秀城二代宅9-2-1501</t>
+  </si>
+  <si>
+    <t>12中</t>
+  </si>
+  <si>
+    <t>80/100</t>
+  </si>
+  <si>
+    <t>/</t>
+  </si>
+  <si>
+    <t>优师帮</t>
   </si>
   <si>
     <t>240/2h</t>
   </si>
   <si>
-    <t>周日10：00-12：00</t>
-  </si>
-  <si>
-    <t>安芯宇</t>
-  </si>
-  <si>
-    <t>文艺路106号 恒福大厦3楼</t>
+    <t>周三20：30-22：30</t>
+  </si>
+  <si>
+    <t>李金翰</t>
+  </si>
+  <si>
+    <t>新医路165号汇文大厦504</t>
+  </si>
+  <si>
+    <t>师大</t>
+  </si>
+  <si>
+    <t>80/150</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>360/1.5h</t>
+  </si>
+  <si>
+    <t>博瑞佰艺</t>
+  </si>
+  <si>
+    <t>每天19：30-21：00</t>
+  </si>
+  <si>
+    <t>徐子洋</t>
+  </si>
+  <si>
+    <t>德泽园三区1-1-202</t>
+  </si>
+  <si>
+    <t>126中学</t>
+  </si>
+  <si>
+    <t>60/100</t>
+  </si>
+  <si>
+    <t>一尔优教育</t>
+  </si>
+  <si>
+    <t>周日18：00-20：00</t>
+  </si>
+  <si>
+    <t>张恒源</t>
+  </si>
+  <si>
+    <t>丹霞山街绿谷学府3-1-403</t>
+  </si>
+  <si>
+    <t>30/150</t>
+  </si>
+  <si>
+    <t>周一20：30-22：30</t>
+  </si>
+  <si>
+    <t>姜弈瞳</t>
+  </si>
+  <si>
+    <t>锦绣三街-和兴帝景4-1-1403</t>
+  </si>
+  <si>
+    <t>108/150</t>
+  </si>
+  <si>
+    <t>物理</t>
+  </si>
+  <si>
+    <t>210/2h</t>
+  </si>
+  <si>
+    <t>周日12：00-14：00</t>
+  </si>
+  <si>
+    <t>柯梓萌</t>
+  </si>
+  <si>
+    <t>青年路国税小区3-1-501</t>
+  </si>
+  <si>
+    <t>40/100</t>
+  </si>
+  <si>
+    <t>周日15：00-17：00</t>
+  </si>
+  <si>
+    <t>刘卓雅</t>
+  </si>
+  <si>
+    <t>邮区中心局小区3-4-602</t>
+  </si>
+  <si>
+    <t>13中</t>
+  </si>
+  <si>
+    <t>李冰惠</t>
+  </si>
+  <si>
+    <t>一中家属院7号院1-2-201</t>
+  </si>
+  <si>
+    <t>120/150</t>
+  </si>
+  <si>
+    <t>周二周四19：20-21：20</t>
+  </si>
+  <si>
+    <t>夏锦程</t>
+  </si>
+  <si>
+    <t>天章大厦</t>
+  </si>
+  <si>
+    <t>19中</t>
+  </si>
+  <si>
+    <t>30/90</t>
+  </si>
+  <si>
+    <t>周三周五19：20-21：20</t>
+  </si>
+  <si>
+    <t>刘东睿</t>
+  </si>
+  <si>
+    <t>11中</t>
+  </si>
+  <si>
+    <t>50/150</t>
+  </si>
+  <si>
+    <t>周六15：00-17：00</t>
+  </si>
+  <si>
+    <t>马金亮</t>
+  </si>
+  <si>
+    <t>复读</t>
+  </si>
+  <si>
+    <t>70/150</t>
+  </si>
+  <si>
+    <t>周六20：00-22：00</t>
+  </si>
+  <si>
+    <t>张育铭</t>
+  </si>
+  <si>
+    <t>金源贸易城5-1-602</t>
+  </si>
+  <si>
+    <t>104团中学</t>
+  </si>
+  <si>
+    <t>100/150</t>
+  </si>
+  <si>
+    <t>周日09：00-11：00</t>
+  </si>
+  <si>
+    <t>周裕民</t>
+  </si>
+  <si>
+    <t>兵二分校</t>
+  </si>
+  <si>
+    <t>高一</t>
+  </si>
+  <si>
+    <t>320/2h</t>
+  </si>
+  <si>
+    <t>周日15：30-17：30</t>
+  </si>
+  <si>
+    <t>吴雨桐</t>
+  </si>
+  <si>
+    <t>丽园路轩和苑C区 3-2-102</t>
+  </si>
+  <si>
+    <t>60/150</t>
+  </si>
+  <si>
+    <t>周六17：10-19：10</t>
+  </si>
+  <si>
+    <t>孙朝(zhao)阳</t>
+  </si>
+  <si>
+    <t>450/2h</t>
+  </si>
+  <si>
+    <t>周六18：30-20：30</t>
+  </si>
+  <si>
+    <t>魏子骞</t>
+  </si>
+  <si>
+    <t>幸福路48号二建小区 9-2-302</t>
+  </si>
+  <si>
+    <t>70/90</t>
+  </si>
+  <si>
+    <t>初一</t>
+  </si>
+  <si>
+    <t>掌学教育</t>
+  </si>
+  <si>
+    <t>220/2h</t>
+  </si>
+  <si>
+    <t>朱思臣</t>
+  </si>
+  <si>
+    <t>新民路29号 3-201</t>
+  </si>
+  <si>
+    <t>90/100</t>
+  </si>
+  <si>
+    <t>精锐教育</t>
+  </si>
+  <si>
+    <t>周日20：00-22：00</t>
+  </si>
+  <si>
+    <t>孙翊原</t>
+  </si>
+  <si>
+    <t>卫生巷88号 6-1-403</t>
+  </si>
+  <si>
+    <t>110/150</t>
+  </si>
+  <si>
+    <t>270/2h</t>
+  </si>
+  <si>
+    <t>周日14：00-16：00</t>
+  </si>
+  <si>
+    <t>贾梦垚</t>
+  </si>
+  <si>
+    <t>德泽园3区1-1-101</t>
+  </si>
+  <si>
+    <t>周六12：00-14：00</t>
+  </si>
+  <si>
+    <t>张佳宁</t>
+  </si>
+  <si>
+    <t>耳鼻喉科专科医院旁巷子201室</t>
   </si>
   <si>
     <t>一中</t>
-  </si>
-  <si>
-    <t>80/100</t>
-  </si>
-  <si>
-    <t>/</t>
-  </si>
-  <si>
-    <t>转账时间(灰色表示线上上课（课时费1小时100），绿色表示课时费已发)：
-一尔优和一对一教育当月1号和15号
-目标：安芯宇：135</t>
-  </si>
-  <si>
-    <t>第11课</t>
-  </si>
-  <si>
-    <t>新耀科技</t>
-  </si>
-  <si>
-    <t>180/1.5h</t>
-  </si>
-  <si>
-    <t>周六19：00-20：30</t>
-  </si>
-  <si>
-    <t>宁芮一</t>
-  </si>
-  <si>
-    <t>光明路北小区14-2-503</t>
-  </si>
-  <si>
-    <t>兵一</t>
-  </si>
-  <si>
-    <t>90/150</t>
-  </si>
-  <si>
-    <t>初二</t>
-  </si>
-  <si>
-    <t>豌豆文化</t>
-  </si>
-  <si>
-    <t>260/2h</t>
-  </si>
-  <si>
-    <t>周六15：30-17：30</t>
-  </si>
-  <si>
-    <t>双胞胎</t>
-  </si>
-  <si>
-    <t>秀城二代宅9-2-1501</t>
-  </si>
-  <si>
-    <t>12中</t>
-  </si>
-  <si>
-    <t>优师帮</t>
-  </si>
-  <si>
-    <t>周三20：30-22：30</t>
-  </si>
-  <si>
-    <t>李金翰</t>
-  </si>
-  <si>
-    <t>新医路165号汇文大厦504</t>
-  </si>
-  <si>
-    <t>师大</t>
-  </si>
-  <si>
-    <t>80/150</t>
-  </si>
-  <si>
-    <t>无</t>
-  </si>
-  <si>
-    <t>360/1.5h</t>
-  </si>
-  <si>
-    <t>博瑞佰艺</t>
-  </si>
-  <si>
-    <t>每天19：30-21：00</t>
-  </si>
-  <si>
-    <t>徐子洋</t>
-  </si>
-  <si>
-    <t>德泽园三区1-1-202</t>
-  </si>
-  <si>
-    <t>126中学</t>
-  </si>
-  <si>
-    <t>60/100</t>
-  </si>
-  <si>
-    <t>一尔优教育</t>
-  </si>
-  <si>
-    <t>周日18：00-20：00</t>
-  </si>
-  <si>
-    <t>张恒源</t>
-  </si>
-  <si>
-    <t>丹霞山街绿谷学府3-1-403</t>
-  </si>
-  <si>
-    <t>30/150</t>
-  </si>
-  <si>
-    <t>周一20：30-22：30</t>
-  </si>
-  <si>
-    <t>姜弈瞳</t>
-  </si>
-  <si>
-    <t>锦绣三街-和兴帝景4-1-1403</t>
-  </si>
-  <si>
-    <t>108/150</t>
-  </si>
-  <si>
-    <t>物理</t>
-  </si>
-  <si>
-    <t>210/2h</t>
-  </si>
-  <si>
-    <t>周日12：00-14：00</t>
-  </si>
-  <si>
-    <t>柯梓萌</t>
-  </si>
-  <si>
-    <t>青年路国税小区3-1-501</t>
-  </si>
-  <si>
-    <t>40/100</t>
-  </si>
-  <si>
-    <t>周日15：00-17：00</t>
-  </si>
-  <si>
-    <t>刘卓雅</t>
-  </si>
-  <si>
-    <t>邮区中心局小区3-4-602</t>
-  </si>
-  <si>
-    <t>13中</t>
-  </si>
-  <si>
-    <t>李冰惠</t>
-  </si>
-  <si>
-    <t>一中家属院7号院1-2-201</t>
-  </si>
-  <si>
-    <t>120/150</t>
-  </si>
-  <si>
-    <t>周二周四19：20-21：20</t>
-  </si>
-  <si>
-    <t>夏锦程</t>
-  </si>
-  <si>
-    <t>天章大厦</t>
-  </si>
-  <si>
-    <t>19中</t>
-  </si>
-  <si>
-    <t>30/90</t>
-  </si>
-  <si>
-    <t>周三周五19：20-21：20</t>
-  </si>
-  <si>
-    <t>刘东睿</t>
-  </si>
-  <si>
-    <t>11中</t>
-  </si>
-  <si>
-    <t>50/150</t>
-  </si>
-  <si>
-    <t>周六15：00-17：00</t>
-  </si>
-  <si>
-    <t>马金亮</t>
-  </si>
-  <si>
-    <t>复读</t>
-  </si>
-  <si>
-    <t>70/150</t>
-  </si>
-  <si>
-    <t>周六20：00-22：00</t>
-  </si>
-  <si>
-    <t>张育铭</t>
-  </si>
-  <si>
-    <t>金源贸易城5-1-602</t>
-  </si>
-  <si>
-    <t>104团中学</t>
-  </si>
-  <si>
-    <t>100/150</t>
-  </si>
-  <si>
-    <t>周日09：00-11：00</t>
-  </si>
-  <si>
-    <t>周裕民</t>
-  </si>
-  <si>
-    <t>兵二分校</t>
-  </si>
-  <si>
-    <t>高一</t>
-  </si>
-  <si>
-    <t>320/2h</t>
-  </si>
-  <si>
-    <t>周日15：30-17：30</t>
-  </si>
-  <si>
-    <t>吴雨桐</t>
-  </si>
-  <si>
-    <t>丽园路轩和苑C区 3-2-102</t>
-  </si>
-  <si>
-    <t>60/150</t>
-  </si>
-  <si>
-    <t>周六17：10-19：10</t>
-  </si>
-  <si>
-    <t>孙朝(zhao)阳</t>
-  </si>
-  <si>
-    <t>450/2h</t>
-  </si>
-  <si>
-    <t>周六18：30-20：30</t>
-  </si>
-  <si>
-    <t>魏子骞</t>
-  </si>
-  <si>
-    <t>幸福路48号二建小区 9-2-302</t>
-  </si>
-  <si>
-    <t>70/90</t>
-  </si>
-  <si>
-    <t>初一</t>
-  </si>
-  <si>
-    <t>掌学教育</t>
-  </si>
-  <si>
-    <t>220/2h</t>
-  </si>
-  <si>
-    <t>朱思臣</t>
-  </si>
-  <si>
-    <t>新民路29号 3-201</t>
-  </si>
-  <si>
-    <t>90/100</t>
-  </si>
-  <si>
-    <t>精锐教育</t>
-  </si>
-  <si>
-    <t>周日20：00-22：00</t>
-  </si>
-  <si>
-    <t>孙翊原</t>
-  </si>
-  <si>
-    <t>卫生巷88号 6-1-403</t>
-  </si>
-  <si>
-    <t>110/150</t>
-  </si>
-  <si>
-    <t>270/2h</t>
-  </si>
-  <si>
-    <t>周日14：00-16：00</t>
-  </si>
-  <si>
-    <t>贾梦垚</t>
-  </si>
-  <si>
-    <t>德泽园3区1-1-101</t>
-  </si>
-  <si>
-    <t>周六12：00-14：00</t>
-  </si>
-  <si>
-    <t>张佳宁</t>
-  </si>
-  <si>
-    <t>耳鼻喉科专科医院旁巷子201室</t>
   </si>
   <si>
     <t>85/100</t>
@@ -528,6 +516,18 @@
   </si>
   <si>
     <t>130/150</t>
+  </si>
+  <si>
+    <t>一对一教育</t>
+  </si>
+  <si>
+    <t>周日10：00-12：00</t>
+  </si>
+  <si>
+    <t>安芯宇</t>
+  </si>
+  <si>
+    <t>文艺路106号 恒福大厦3楼</t>
   </si>
   <si>
     <t xml:space="preserve">绿色表示课时费已发；
@@ -1590,21 +1590,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:T22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="5.37272727272727" customWidth="1"/>
-    <col min="3" max="3" width="11.1818181818182" customWidth="1"/>
-    <col min="4" max="4" width="7.87272727272727" customWidth="1"/>
+    <col min="1" max="2" width="5.375" customWidth="1"/>
+    <col min="3" max="3" width="11.1833333333333" customWidth="1"/>
+    <col min="4" max="4" width="7.875" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="6.87272727272727" customWidth="1"/>
-    <col min="7" max="7" width="24.2545454545455" customWidth="1"/>
-    <col min="8" max="8" width="6.12727272727273" customWidth="1"/>
-    <col min="9" max="9" width="9.12727272727273" customWidth="1"/>
-    <col min="10" max="10" width="10.8363636363636" customWidth="1"/>
+    <col min="6" max="6" width="6.875" customWidth="1"/>
+    <col min="7" max="7" width="24.2583333333333" customWidth="1"/>
+    <col min="8" max="8" width="6.125" customWidth="1"/>
+    <col min="9" max="9" width="9.125" customWidth="1"/>
+    <col min="10" max="10" width="10.8333333333333" customWidth="1"/>
     <col min="11" max="20" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:20">
+    <row r="1" ht="15.75" spans="1:20">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1666,101 +1666,14 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" customFormat="1" ht="15" spans="1:20">
-      <c r="A2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" s="21">
-        <v>46004</v>
-      </c>
-      <c r="L2" s="21">
-        <v>46011</v>
-      </c>
-      <c r="M2" s="21">
-        <v>46018</v>
-      </c>
-      <c r="N2" s="21">
-        <v>46025</v>
-      </c>
-      <c r="O2" s="21">
-        <v>46032</v>
-      </c>
-      <c r="P2" s="21">
-        <v>46039</v>
-      </c>
-      <c r="Q2" s="21">
-        <v>46046</v>
-      </c>
-      <c r="R2" s="21">
-        <v>46116</v>
-      </c>
-      <c r="S2" s="21">
-        <v>46123</v>
-      </c>
-      <c r="T2" s="21">
-        <v>46131</v>
-      </c>
-    </row>
-    <row r="3" ht="15" spans="1:15">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21">
-        <v>46138</v>
-      </c>
-      <c r="L3" s="21">
-        <v>46143</v>
-      </c>
-      <c r="M3" s="21">
-        <v>46152</v>
-      </c>
-      <c r="N3" s="22">
-        <v>46159</v>
-      </c>
-      <c r="O3" s="22">
-        <v>46166</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" ht="15"/>
-    <row r="12" s="2" customFormat="1" ht="15"/>
-    <row r="13" s="2" customFormat="1" ht="15"/>
-    <row r="14" s="2" customFormat="1" ht="15"/>
-    <row r="15" s="2" customFormat="1" ht="15"/>
-    <row r="16" s="2" customFormat="1" ht="15" spans="1:9">
+    <row r="2" customFormat="1"/>
+    <row r="3" customFormat="1"/>
+    <row r="11" s="2" customFormat="1" ht="15.75"/>
+    <row r="12" s="2" customFormat="1" ht="15.75"/>
+    <row r="13" s="2" customFormat="1" ht="15.75"/>
+    <row r="14" s="2" customFormat="1" ht="15.75"/>
+    <row r="15" s="2" customFormat="1" ht="15.75"/>
+    <row r="16" s="2" customFormat="1" ht="15.75" spans="1:9">
       <c r="A16" s="28"/>
       <c r="B16" s="28"/>
       <c r="C16" s="28"/>
@@ -1771,7 +1684,7 @@
       <c r="H16" s="28"/>
       <c r="I16" s="28"/>
     </row>
-    <row r="17" s="2" customFormat="1" ht="15" spans="1:9">
+    <row r="17" s="2" customFormat="1" ht="15.75" spans="1:9">
       <c r="A17" s="28"/>
       <c r="B17" s="28"/>
       <c r="C17" s="28"/>
@@ -1782,9 +1695,9 @@
       <c r="H17" s="28"/>
       <c r="I17" s="28"/>
     </row>
-    <row r="18" ht="17.5" spans="2:13">
+    <row r="18" ht="18.75" spans="2:13">
       <c r="B18" s="9" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
@@ -1798,7 +1711,7 @@
       <c r="L18" s="29"/>
       <c r="M18" s="29"/>
     </row>
-    <row r="19" ht="17.5" spans="2:13">
+    <row r="19" ht="18.75" spans="2:13">
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
@@ -1812,7 +1725,7 @@
       <c r="L19" s="29"/>
       <c r="M19" s="29"/>
     </row>
-    <row r="20" ht="17.5" spans="2:12">
+    <row r="20" ht="18.75" spans="2:12">
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
@@ -1824,7 +1737,7 @@
       <c r="K20" s="29"/>
       <c r="L20" s="29"/>
     </row>
-    <row r="21" ht="17.5" spans="2:13">
+    <row r="21" ht="18.75" spans="2:13">
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
@@ -1838,7 +1751,7 @@
       <c r="L21" s="29"/>
       <c r="M21" s="29"/>
     </row>
-    <row r="22" ht="17.5" spans="2:13">
+    <row r="22" ht="18.75" spans="2:13">
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
@@ -1853,17 +1766,7 @@
       <c r="M22" s="29"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
+  <mergeCells count="1">
     <mergeCell ref="B18:I22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1875,23 +1778,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U67"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:U69"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="4.58181818181818" customWidth="1"/>
-    <col min="3" max="3" width="10.8727272727273" customWidth="1"/>
-    <col min="4" max="4" width="17.7272727272727" customWidth="1"/>
-    <col min="5" max="5" width="23.1818181818182" customWidth="1"/>
-    <col min="6" max="6" width="7.33636363636364" customWidth="1"/>
-    <col min="7" max="7" width="27.1272727272727" customWidth="1"/>
-    <col min="8" max="9" width="9.58181818181818" customWidth="1"/>
-    <col min="10" max="10" width="10.6272727272727" customWidth="1"/>
-    <col min="11" max="20" width="11.2727272727273" customWidth="1"/>
-    <col min="21" max="21" width="10.7545454545455" customWidth="1"/>
+    <col min="1" max="2" width="4.58333333333333" customWidth="1"/>
+    <col min="3" max="3" width="10.875" customWidth="1"/>
+    <col min="4" max="4" width="17.725" customWidth="1"/>
+    <col min="5" max="5" width="23.1833333333333" customWidth="1"/>
+    <col min="6" max="6" width="7.33333333333333" customWidth="1"/>
+    <col min="7" max="7" width="27.125" customWidth="1"/>
+    <col min="8" max="9" width="9.58333333333333" customWidth="1"/>
+    <col min="10" max="10" width="10.625" customWidth="1"/>
+    <col min="11" max="20" width="11.275" customWidth="1"/>
+    <col min="21" max="21" width="10.7583333333333" customWidth="1"/>
     <col min="22" max="23" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:21">
+    <row r="1" ht="15.75" spans="1:21">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1953,36 +1856,36 @@
         <v>19</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" customFormat="1" ht="15" spans="1:21">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="15.75" spans="1:21">
       <c r="A2" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J2" s="10">
         <v>45185</v>
@@ -2021,36 +1924,36 @@
         <v>45248</v>
       </c>
     </row>
-    <row r="3" customFormat="1" ht="15" spans="1:19">
+    <row r="3" customFormat="1" ht="15.75" spans="1:19">
       <c r="A3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" s="10" t="s">
         <v>39</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>29</v>
       </c>
       <c r="K3" s="10">
         <v>45248</v>
@@ -2080,33 +1983,33 @@
         <v>45304</v>
       </c>
     </row>
-    <row r="4" customFormat="1" ht="15" spans="1:11">
+    <row r="4" customFormat="1" ht="15.75" spans="1:11">
       <c r="A4" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>51</v>
       </c>
       <c r="J4" s="10">
         <v>45287</v>
@@ -2115,36 +2018,36 @@
         <v>45294</v>
       </c>
     </row>
-    <row r="5" customFormat="1" ht="15" spans="1:20">
+    <row r="5" customFormat="1" ht="15.75" spans="1:20">
       <c r="A5" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="K5" s="10">
         <v>45255</v>
@@ -2175,33 +2078,33 @@
       </c>
       <c r="T5" s="1"/>
     </row>
-    <row r="6" customFormat="1" ht="15" spans="1:20">
+    <row r="6" customFormat="1" ht="15.75" spans="1:20">
       <c r="A6" s="5" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="I6" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="J6" s="10">
         <v>45320</v>
@@ -2237,36 +2140,36 @@
         <v>45344</v>
       </c>
     </row>
-    <row r="7" customFormat="1" ht="15" spans="1:20">
+    <row r="7" customFormat="1" ht="15.75" spans="1:20">
       <c r="A7" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="K7" s="13">
         <v>45361</v>
@@ -2285,31 +2188,31 @@
     </row>
     <row r="8" customFormat="1" ht="17" customHeight="1" spans="1:20">
       <c r="A8" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="H8" s="7">
         <v>126</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="J8" s="15">
         <v>45425</v>
@@ -2324,33 +2227,33 @@
       <c r="S8" s="4"/>
       <c r="T8" s="4"/>
     </row>
-    <row r="9" customFormat="1" ht="15" spans="1:20">
+    <row r="9" customFormat="1" ht="15.75" spans="1:20">
       <c r="A9" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="5" t="s">
         <v>69</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>74</v>
       </c>
       <c r="J9" s="10">
         <v>45186</v>
@@ -2386,7 +2289,7 @@
         <v>45263</v>
       </c>
     </row>
-    <row r="10" customFormat="1" ht="15" spans="1:20">
+    <row r="10" customFormat="1" ht="15.75" spans="1:20">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -2428,7 +2331,7 @@
         <v>45354</v>
       </c>
     </row>
-    <row r="11" customFormat="1" ht="15" spans="1:20">
+    <row r="11" customFormat="1" ht="15.75" spans="1:20">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -2470,7 +2373,7 @@
         <v>45445</v>
       </c>
     </row>
-    <row r="12" customFormat="1" ht="15" spans="1:20">
+    <row r="12" customFormat="1" ht="15.75" spans="1:20">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -2494,36 +2397,36 @@
       <c r="S12" s="19"/>
       <c r="T12" s="19"/>
     </row>
-    <row r="13" customFormat="1" ht="15" spans="1:20">
+    <row r="13" customFormat="1" ht="15.75" spans="1:20">
       <c r="A13" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J13" s="18" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="K13" s="16">
         <v>45382</v>
@@ -2556,7 +2459,7 @@
         <v>45453</v>
       </c>
     </row>
-    <row r="14" customFormat="1" ht="15" spans="1:20">
+    <row r="14" customFormat="1" ht="15.75" spans="1:20">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -2580,36 +2483,36 @@
       <c r="S14" s="17"/>
       <c r="T14" s="19"/>
     </row>
-    <row r="15" customFormat="1" ht="15" spans="1:20">
+    <row r="15" customFormat="1" ht="15.75" spans="1:20">
       <c r="A15" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="K15" s="13">
         <v>45413</v>
@@ -2636,36 +2539,36 @@
       <c r="S15" s="17"/>
       <c r="T15" s="19"/>
     </row>
-    <row r="16" customFormat="1" ht="15" spans="1:20">
+    <row r="16" customFormat="1" ht="15.75" spans="1:20">
       <c r="A16" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="K16" s="13">
         <v>45426</v>
@@ -2698,36 +2601,36 @@
         <v>45461</v>
       </c>
     </row>
-    <row r="17" customFormat="1" ht="15" spans="1:20">
+    <row r="17" customFormat="1" ht="15.75" spans="1:20">
       <c r="A17" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G17" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="H17" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="H17" s="5" t="s">
-        <v>89</v>
-      </c>
       <c r="I17" s="5" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="J17" s="18" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="K17" s="13">
         <v>45364</v>
@@ -2760,7 +2663,7 @@
         <v>45400</v>
       </c>
     </row>
-    <row r="18" customFormat="1" ht="15" spans="1:20">
+    <row r="18" customFormat="1" ht="15.75" spans="1:20">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -2792,36 +2695,36 @@
       <c r="S18" s="17"/>
       <c r="T18" s="17"/>
     </row>
-    <row r="19" customFormat="1" ht="15" spans="1:20">
+    <row r="19" customFormat="1" ht="15.75" spans="1:20">
       <c r="A19" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="J19" s="18" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="K19" s="13">
         <v>45367</v>
@@ -2854,7 +2757,7 @@
         <v>45451</v>
       </c>
     </row>
-    <row r="20" customFormat="1" ht="15" spans="1:20">
+    <row r="20" customFormat="1" ht="15.75" spans="1:20">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -2886,36 +2789,36 @@
       <c r="S20" s="17"/>
       <c r="T20" s="17"/>
     </row>
-    <row r="21" customFormat="1" ht="15" spans="1:20">
+    <row r="21" customFormat="1" ht="15.75" spans="1:20">
       <c r="A21" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="K21" s="13">
         <v>45234</v>
@@ -2948,7 +2851,7 @@
         <v>45311</v>
       </c>
     </row>
-    <row r="22" customFormat="1" ht="15" spans="1:20">
+    <row r="22" customFormat="1" ht="15.75" spans="1:20">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -2990,7 +2893,7 @@
         <v>45423</v>
       </c>
     </row>
-    <row r="23" customFormat="1" ht="15" spans="1:20">
+    <row r="23" customFormat="1" ht="15.75" spans="1:20">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -3022,36 +2925,36 @@
       <c r="S23" s="19"/>
       <c r="T23" s="19"/>
     </row>
-    <row r="24" customFormat="1" ht="15" spans="1:20">
+    <row r="24" customFormat="1" ht="15.75" spans="1:20">
       <c r="A24" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="J24" s="20" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="K24" s="13">
         <v>45214</v>
@@ -3084,7 +2987,7 @@
         <v>45325</v>
       </c>
     </row>
-    <row r="25" customFormat="1" ht="15" spans="1:20">
+    <row r="25" customFormat="1" ht="15.75" spans="1:20">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -3126,7 +3029,7 @@
         <v>45354</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" ht="15" spans="1:20">
+    <row r="26" s="1" customFormat="1" ht="15.75" spans="1:20">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -3164,36 +3067,36 @@
       <c r="S26" s="17"/>
       <c r="T26" s="17"/>
     </row>
-    <row r="27" customFormat="1" ht="15" spans="1:20">
+    <row r="27" customFormat="1" ht="15.75" spans="1:20">
       <c r="A27" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I27" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>108</v>
-      </c>
       <c r="J27" s="13" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="K27" s="10">
         <v>45551</v>
@@ -3208,36 +3111,36 @@
       <c r="S27" s="25"/>
       <c r="T27" s="25"/>
     </row>
-    <row r="28" customFormat="1" ht="15" spans="1:20">
+    <row r="28" customFormat="1" ht="15.75" spans="1:20">
       <c r="A28" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="J28" s="13" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="K28" s="13">
         <v>45430</v>
@@ -3262,36 +3165,36 @@
       <c r="S28" s="17"/>
       <c r="T28" s="17"/>
     </row>
-    <row r="29" customFormat="1" ht="15" spans="1:18">
+    <row r="29" customFormat="1" ht="15.75" spans="1:18">
       <c r="A29" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="J29" s="13" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="K29" s="13">
         <v>45552</v>
@@ -3304,33 +3207,33 @@
       <c r="Q29" s="17"/>
       <c r="R29" s="17"/>
     </row>
-    <row r="30" customFormat="1" ht="15" spans="1:20">
+    <row r="30" customFormat="1" ht="15.75" spans="1:20">
       <c r="A30" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I30" s="5" t="s">
         <v>116</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>121</v>
       </c>
       <c r="J30" s="10">
         <v>45543</v>
@@ -3358,36 +3261,36 @@
       <c r="S30" s="2"/>
       <c r="T30" s="2"/>
     </row>
-    <row r="31" customFormat="1" ht="15" spans="1:20">
+    <row r="31" customFormat="1" ht="15.75" spans="1:20">
       <c r="A31" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D31" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E31" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E31" s="6" t="s">
-        <v>123</v>
-      </c>
       <c r="F31" s="5" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="J31" s="13" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="K31" s="13">
         <v>45543</v>
@@ -3420,36 +3323,36 @@
         <v>45627</v>
       </c>
     </row>
-    <row r="32" customFormat="1" ht="15" spans="1:20">
+    <row r="32" customFormat="1" ht="15.75" spans="1:20">
       <c r="A32" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="J32" s="13" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="K32" s="21">
         <v>45557</v>
@@ -3482,7 +3385,7 @@
         <v>45627</v>
       </c>
     </row>
-    <row r="33" customFormat="1" ht="15" spans="1:20">
+    <row r="33" customFormat="1" ht="15.75" spans="1:20">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -3510,36 +3413,36 @@
       <c r="S33" s="22"/>
       <c r="T33" s="22"/>
     </row>
-    <row r="34" customFormat="1" ht="15" spans="1:20">
+    <row r="34" customFormat="1" ht="15.75" spans="1:20">
       <c r="A34" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="J34" s="13" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="K34" s="13">
         <v>45451</v>
@@ -3566,36 +3469,36 @@
       <c r="S34" s="17"/>
       <c r="T34" s="17"/>
     </row>
-    <row r="35" customFormat="1" ht="15" spans="1:20">
+    <row r="35" customFormat="1" ht="15.75" spans="1:20">
       <c r="A35" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D35" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="H35" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="I35" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="F35" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="I35" s="5" t="s">
-        <v>140</v>
-      </c>
       <c r="J35" s="23" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="K35" s="21">
         <v>45643</v>
@@ -3628,7 +3531,7 @@
         <v>45670</v>
       </c>
     </row>
-    <row r="36" customFormat="1" ht="15" spans="1:20">
+    <row r="36" customFormat="1" ht="15.75" spans="1:20">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -3670,7 +3573,7 @@
         <v>45691</v>
       </c>
     </row>
-    <row r="37" customFormat="1" ht="15" spans="1:20">
+    <row r="37" customFormat="1" ht="15.75" spans="1:20">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -3712,7 +3615,7 @@
         <v>45712</v>
       </c>
     </row>
-    <row r="38" customFormat="1" ht="15" spans="1:20">
+    <row r="38" customFormat="1" ht="15.75" spans="1:20">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -3741,36 +3644,36 @@
       <c r="S38" s="22"/>
       <c r="T38" s="22"/>
     </row>
-    <row r="39" customFormat="1" ht="15" spans="1:20">
+    <row r="39" customFormat="1" ht="15.75" spans="1:20">
       <c r="A39" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H39" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="I39" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="I39" s="5" t="s">
-        <v>143</v>
-      </c>
       <c r="J39" s="10" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="K39" s="21">
         <v>45551</v>
@@ -3803,7 +3706,7 @@
         <v>45592</v>
       </c>
     </row>
-    <row r="40" customFormat="1" ht="15" spans="1:20">
+    <row r="40" customFormat="1" ht="15.75" spans="1:20">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -3845,7 +3748,7 @@
         <v>45718</v>
       </c>
     </row>
-    <row r="41" customFormat="1" ht="15" spans="1:13">
+    <row r="41" customFormat="1" ht="15.75" spans="1:13">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -3866,33 +3769,33 @@
         <v>45746</v>
       </c>
     </row>
-    <row r="42" customFormat="1" ht="15" spans="1:20">
+    <row r="42" customFormat="1" ht="15.75" spans="1:20">
       <c r="A42" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="J42" s="21">
         <v>45556</v>
@@ -3928,7 +3831,7 @@
         <v>45623</v>
       </c>
     </row>
-    <row r="43" customFormat="1" ht="15" spans="1:20">
+    <row r="43" customFormat="1" ht="15.75" spans="1:20">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -3970,7 +3873,7 @@
         <v>45703</v>
       </c>
     </row>
-    <row r="44" customFormat="1" ht="15" spans="1:20">
+    <row r="44" customFormat="1" ht="15.75" spans="1:20">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -4008,31 +3911,31 @@
     </row>
     <row r="45" customFormat="1" ht="16" customHeight="1" spans="1:20">
       <c r="A45" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C45" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="H45" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="I45" s="5" t="s">
         <v>148</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="H45" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="I45" s="5" t="s">
-        <v>152</v>
       </c>
       <c r="J45" s="21">
         <v>45778</v>
@@ -4048,36 +3951,36 @@
       <c r="S45" s="22"/>
       <c r="T45" s="22"/>
     </row>
-    <row r="46" customFormat="1" ht="15" spans="1:20">
+    <row r="46" customFormat="1" ht="15.75" spans="1:20">
       <c r="A46" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="K46" s="24">
         <v>45551</v>
@@ -4110,7 +4013,7 @@
         <v>45620</v>
       </c>
     </row>
-    <row r="47" customFormat="1" ht="15" spans="1:20">
+    <row r="47" customFormat="1" ht="15.75" spans="1:20">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -4152,7 +4055,7 @@
         <v>45746</v>
       </c>
     </row>
-    <row r="48" customFormat="1" ht="15" spans="1:20">
+    <row r="48" customFormat="1" ht="15.75" spans="1:20">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -4184,36 +4087,36 @@
       <c r="S48" s="22"/>
       <c r="T48" s="22"/>
     </row>
-    <row r="49" s="2" customFormat="1" ht="15" spans="1:16">
+    <row r="49" s="2" customFormat="1" ht="15.75" spans="1:16">
       <c r="A49" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E49" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="I49" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="F49" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="H49" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="I49" s="5" t="s">
-        <v>160</v>
-      </c>
       <c r="J49" s="20" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="K49" s="21">
         <v>45781</v>
@@ -4234,33 +4137,33 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="50" customFormat="1" ht="15" spans="1:20">
+    <row r="50" customFormat="1" ht="15.75" spans="1:20">
       <c r="A50" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E50" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="I50" s="5" t="s">
         <v>161</v>
-      </c>
-      <c r="F50" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="H50" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="I50" s="5" t="s">
-        <v>165</v>
       </c>
       <c r="J50" s="21">
         <v>45710</v>
@@ -4296,7 +4199,7 @@
         <v>45746</v>
       </c>
     </row>
-    <row r="51" customFormat="1" ht="15" spans="1:20">
+    <row r="51" customFormat="1" ht="15.75" spans="1:20">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -4338,7 +4241,7 @@
         <v>45787</v>
       </c>
     </row>
-    <row r="52" customFormat="1" ht="15" spans="1:20">
+    <row r="52" customFormat="1" ht="15.75" spans="1:20">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -4380,33 +4283,33 @@
         <v>45822</v>
       </c>
     </row>
-    <row r="53" customFormat="1" ht="15" spans="1:12">
+    <row r="53" customFormat="1" ht="15.75" spans="1:12">
       <c r="A53" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="J53" s="21">
         <v>45810</v>
@@ -4418,29 +4321,69 @@
         <v>45817</v>
       </c>
     </row>
-    <row r="54" customFormat="1" ht="15" spans="1:20">
-      <c r="A54" s="5"/>
-      <c r="B54" s="5"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
-      <c r="H54" s="5"/>
-      <c r="I54" s="5"/>
-      <c r="J54" s="22"/>
-      <c r="K54" s="22"/>
-      <c r="L54" s="22"/>
-      <c r="M54" s="22"/>
-      <c r="N54" s="22"/>
-      <c r="O54" s="22"/>
-      <c r="P54" s="22"/>
-      <c r="Q54" s="22"/>
-      <c r="R54" s="22"/>
-      <c r="S54" s="22"/>
-      <c r="T54" s="22"/>
-    </row>
-    <row r="55" customFormat="1" ht="15" spans="1:20">
+    <row r="54" customFormat="1" ht="15.75" spans="1:20">
+      <c r="A54" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J54" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="K54" s="21">
+        <v>46004</v>
+      </c>
+      <c r="L54" s="21">
+        <v>46011</v>
+      </c>
+      <c r="M54" s="21">
+        <v>46018</v>
+      </c>
+      <c r="N54" s="21">
+        <v>46025</v>
+      </c>
+      <c r="O54" s="21">
+        <v>46032</v>
+      </c>
+      <c r="P54" s="21">
+        <v>46039</v>
+      </c>
+      <c r="Q54" s="21">
+        <v>46046</v>
+      </c>
+      <c r="R54" s="21">
+        <v>46116</v>
+      </c>
+      <c r="S54" s="21">
+        <v>46123</v>
+      </c>
+      <c r="T54" s="21">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="55" customFormat="1" ht="15.75" spans="1:15">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -4450,19 +4393,24 @@
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
-      <c r="J55" s="22"/>
-      <c r="K55" s="22"/>
-      <c r="L55" s="22"/>
-      <c r="M55" s="22"/>
-      <c r="N55" s="22"/>
-      <c r="O55" s="22"/>
-      <c r="P55" s="22"/>
-      <c r="Q55" s="22"/>
-      <c r="R55" s="22"/>
-      <c r="S55" s="22"/>
-      <c r="T55" s="22"/>
-    </row>
-    <row r="56" customFormat="1" ht="15" spans="1:20">
+      <c r="J55" s="21"/>
+      <c r="K55" s="21">
+        <v>46138</v>
+      </c>
+      <c r="L55" s="21">
+        <v>46143</v>
+      </c>
+      <c r="M55" s="21">
+        <v>46152</v>
+      </c>
+      <c r="N55" s="21">
+        <v>46159</v>
+      </c>
+      <c r="O55" s="21">
+        <v>46166</v>
+      </c>
+    </row>
+    <row r="56" customFormat="1" ht="15.75" spans="1:20">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -4484,7 +4432,7 @@
       <c r="S56" s="22"/>
       <c r="T56" s="22"/>
     </row>
-    <row r="57" customFormat="1" ht="15" spans="1:20">
+    <row r="57" customFormat="1" ht="15.75" spans="1:20">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -4506,51 +4454,51 @@
       <c r="S57" s="22"/>
       <c r="T57" s="22"/>
     </row>
-    <row r="58" customFormat="1" ht="15" spans="1:20">
+    <row r="58" customFormat="1" ht="15.75" spans="1:20">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
-      <c r="E58" s="5"/>
+      <c r="E58" s="8"/>
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
-      <c r="J58" s="25"/>
-      <c r="K58" s="25"/>
-      <c r="L58" s="25"/>
-      <c r="M58" s="25"/>
-      <c r="N58" s="25"/>
-      <c r="O58" s="25"/>
-      <c r="P58" s="25"/>
-      <c r="Q58" s="25"/>
-      <c r="R58" s="25"/>
-      <c r="S58" s="27"/>
-      <c r="T58" s="27"/>
-    </row>
-    <row r="59" customFormat="1" ht="15" spans="1:20">
+      <c r="J58" s="22"/>
+      <c r="K58" s="22"/>
+      <c r="L58" s="22"/>
+      <c r="M58" s="22"/>
+      <c r="N58" s="22"/>
+      <c r="O58" s="22"/>
+      <c r="P58" s="22"/>
+      <c r="Q58" s="22"/>
+      <c r="R58" s="22"/>
+      <c r="S58" s="22"/>
+      <c r="T58" s="22"/>
+    </row>
+    <row r="59" customFormat="1" ht="15.75" spans="1:20">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
-      <c r="E59" s="5"/>
+      <c r="E59" s="8"/>
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
-      <c r="J59" s="25"/>
-      <c r="K59" s="25"/>
-      <c r="L59" s="25"/>
-      <c r="M59" s="25"/>
-      <c r="N59" s="25"/>
-      <c r="O59" s="25"/>
-      <c r="P59" s="25"/>
-      <c r="Q59" s="25"/>
-      <c r="R59" s="25"/>
-      <c r="S59" s="27"/>
-      <c r="T59" s="27"/>
-    </row>
-    <row r="60" customFormat="1" ht="15" spans="1:20">
+      <c r="J59" s="22"/>
+      <c r="K59" s="22"/>
+      <c r="L59" s="22"/>
+      <c r="M59" s="22"/>
+      <c r="N59" s="22"/>
+      <c r="O59" s="22"/>
+      <c r="P59" s="22"/>
+      <c r="Q59" s="22"/>
+      <c r="R59" s="22"/>
+      <c r="S59" s="22"/>
+      <c r="T59" s="22"/>
+    </row>
+    <row r="60" customFormat="1" ht="15.75" spans="1:20">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -4572,34 +4520,54 @@
       <c r="S60" s="27"/>
       <c r="T60" s="27"/>
     </row>
-    <row r="61" spans="2:11">
-      <c r="B61" s="9" t="s">
+    <row r="61" customFormat="1" ht="15.75" spans="1:20">
+      <c r="A61" s="5"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="5"/>
+      <c r="J61" s="25"/>
+      <c r="K61" s="25"/>
+      <c r="L61" s="25"/>
+      <c r="M61" s="25"/>
+      <c r="N61" s="25"/>
+      <c r="O61" s="25"/>
+      <c r="P61" s="25"/>
+      <c r="Q61" s="25"/>
+      <c r="R61" s="25"/>
+      <c r="S61" s="27"/>
+      <c r="T61" s="27"/>
+    </row>
+    <row r="62" customFormat="1" ht="15.75" spans="1:20">
+      <c r="A62" s="5"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="5"/>
+      <c r="F62" s="5"/>
+      <c r="G62" s="5"/>
+      <c r="H62" s="5"/>
+      <c r="I62" s="5"/>
+      <c r="J62" s="25"/>
+      <c r="K62" s="25"/>
+      <c r="L62" s="25"/>
+      <c r="M62" s="25"/>
+      <c r="N62" s="25"/>
+      <c r="O62" s="25"/>
+      <c r="P62" s="25"/>
+      <c r="Q62" s="25"/>
+      <c r="R62" s="25"/>
+      <c r="S62" s="27"/>
+      <c r="T62" s="27"/>
+    </row>
+    <row r="63" spans="2:11">
+      <c r="B63" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="C61" s="9"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="9"/>
-      <c r="F61" s="9"/>
-      <c r="G61" s="9"/>
-      <c r="H61" s="9"/>
-      <c r="I61" s="9"/>
-      <c r="J61" s="9"/>
-      <c r="K61" s="9"/>
-    </row>
-    <row r="62" spans="2:11">
-      <c r="B62" s="9"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="9"/>
-      <c r="F62" s="9"/>
-      <c r="G62" s="9"/>
-      <c r="H62" s="9"/>
-      <c r="I62" s="9"/>
-      <c r="J62" s="9"/>
-      <c r="K62" s="9"/>
-    </row>
-    <row r="63" spans="2:11">
-      <c r="B63" s="9"/>
       <c r="C63" s="9"/>
       <c r="D63" s="9"/>
       <c r="E63" s="9"/>
@@ -4658,8 +4626,32 @@
       <c r="J67" s="9"/>
       <c r="K67" s="9"/>
     </row>
+    <row r="68" spans="2:11">
+      <c r="B68" s="9"/>
+      <c r="C68" s="9"/>
+      <c r="D68" s="9"/>
+      <c r="E68" s="9"/>
+      <c r="F68" s="9"/>
+      <c r="G68" s="9"/>
+      <c r="H68" s="9"/>
+      <c r="I68" s="9"/>
+      <c r="J68" s="9"/>
+      <c r="K68" s="9"/>
+    </row>
+    <row r="69" spans="2:11">
+      <c r="B69" s="9"/>
+      <c r="C69" s="9"/>
+      <c r="D69" s="9"/>
+      <c r="E69" s="9"/>
+      <c r="F69" s="9"/>
+      <c r="G69" s="9"/>
+      <c r="H69" s="9"/>
+      <c r="I69" s="9"/>
+      <c r="J69" s="9"/>
+      <c r="K69" s="9"/>
+    </row>
   </sheetData>
-  <mergeCells count="120">
+  <mergeCells count="130">
     <mergeCell ref="A9:A12"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="A17:A18"/>
@@ -4672,6 +4664,7 @@
     <mergeCell ref="A42:A44"/>
     <mergeCell ref="A46:A48"/>
     <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A54:A55"/>
     <mergeCell ref="B9:B12"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="B17:B18"/>
@@ -4684,6 +4677,7 @@
     <mergeCell ref="B42:B44"/>
     <mergeCell ref="B46:B48"/>
     <mergeCell ref="B50:B52"/>
+    <mergeCell ref="B54:B55"/>
     <mergeCell ref="C9:C12"/>
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="C17:C18"/>
@@ -4696,6 +4690,7 @@
     <mergeCell ref="C42:C44"/>
     <mergeCell ref="C46:C48"/>
     <mergeCell ref="C50:C52"/>
+    <mergeCell ref="C54:C55"/>
     <mergeCell ref="D9:D12"/>
     <mergeCell ref="D13:D14"/>
     <mergeCell ref="D17:D18"/>
@@ -4708,6 +4703,7 @@
     <mergeCell ref="D42:D44"/>
     <mergeCell ref="D46:D48"/>
     <mergeCell ref="D50:D52"/>
+    <mergeCell ref="D54:D55"/>
     <mergeCell ref="E9:E12"/>
     <mergeCell ref="E13:E14"/>
     <mergeCell ref="E17:E18"/>
@@ -4720,6 +4716,7 @@
     <mergeCell ref="E42:E44"/>
     <mergeCell ref="E46:E48"/>
     <mergeCell ref="E50:E52"/>
+    <mergeCell ref="E54:E55"/>
     <mergeCell ref="F9:F12"/>
     <mergeCell ref="F13:F14"/>
     <mergeCell ref="F17:F18"/>
@@ -4732,6 +4729,7 @@
     <mergeCell ref="F42:F44"/>
     <mergeCell ref="F46:F48"/>
     <mergeCell ref="F50:F52"/>
+    <mergeCell ref="F54:F55"/>
     <mergeCell ref="G9:G12"/>
     <mergeCell ref="G13:G14"/>
     <mergeCell ref="G17:G18"/>
@@ -4744,6 +4742,7 @@
     <mergeCell ref="G42:G44"/>
     <mergeCell ref="G46:G48"/>
     <mergeCell ref="G50:G52"/>
+    <mergeCell ref="G54:G55"/>
     <mergeCell ref="H9:H12"/>
     <mergeCell ref="H13:H14"/>
     <mergeCell ref="H17:H18"/>
@@ -4756,6 +4755,7 @@
     <mergeCell ref="H42:H44"/>
     <mergeCell ref="H46:H48"/>
     <mergeCell ref="H50:H52"/>
+    <mergeCell ref="H54:H55"/>
     <mergeCell ref="I9:I12"/>
     <mergeCell ref="I13:I14"/>
     <mergeCell ref="I17:I18"/>
@@ -4768,6 +4768,7 @@
     <mergeCell ref="I42:I44"/>
     <mergeCell ref="I46:I48"/>
     <mergeCell ref="I50:I52"/>
+    <mergeCell ref="I54:I55"/>
     <mergeCell ref="J9:J12"/>
     <mergeCell ref="J13:J14"/>
     <mergeCell ref="J17:J18"/>
@@ -4779,7 +4780,8 @@
     <mergeCell ref="J42:J44"/>
     <mergeCell ref="J46:J48"/>
     <mergeCell ref="J50:J52"/>
-    <mergeCell ref="B61:K67"/>
+    <mergeCell ref="J54:J55"/>
+    <mergeCell ref="B63:K69"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
